--- a/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_rms_summary.xlsx
+++ b/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_rms_summary.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71C28A0-A139-421F-A481-68B248BE0F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7654" yWindow="5426" windowWidth="24686" windowHeight="13054" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7654" yWindow="5426" windowWidth="24686" windowHeight="13054"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="10">
   <si>
     <t>Frequency Band</t>
   </si>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="4">
     <font>
       <sz val="11"/>
@@ -102,18 +102,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.5999938962981"/>
+        <bgColor theme="8" tint="0.5999938962981"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.79998168889431"/>
+        <bgColor theme="8" tint="0.79998168889431"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -232,48 +232,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -292,7 +294,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -443,7 +445,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -467,9 +469,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -493,7 +495,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -528,7 +530,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -546,7 +548,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -571,7 +573,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -587,20 +589,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.84375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.3828125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.84375" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="15.15234375" bestFit="true" customWidth="true"/>
+    <col min="3" max="3" width="13.765625" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="14" bestFit="true" customWidth="true"/>
+    <col min="5" max="5" width="16.61328125" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="15.23046875" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="14" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.3" thickBot="1">
+    <row r="1" ht="16.3" thickBot="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +613,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>7</v>
@@ -623,73 +625,73 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1">
+    <row r="2" ht="15" thickTop="true">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>49.186</v>
+        <v>48.899999999999999</v>
       </c>
       <c r="C2" s="5">
-        <v>4.6420000000000003</v>
+        <v>4.641</v>
       </c>
       <c r="D2" s="5">
-        <v>90.561999999999998</v>
+        <v>90.509</v>
       </c>
       <c r="E2" s="5">
-        <v>358.99099999999999</v>
+        <v>356.99099999999999</v>
       </c>
       <c r="F2" s="5">
-        <v>310.21600000000001</v>
+        <v>302.88</v>
       </c>
       <c r="G2" s="6">
-        <v>13.587</v>
+        <v>15.157999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3">
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="8">
-        <v>15.794</v>
+        <v>15.624000000000001</v>
       </c>
       <c r="C3" s="8">
-        <v>0.36599999999999999</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="D3" s="8">
         <v>97.685000000000002</v>
       </c>
       <c r="E3" s="8">
-        <v>1.921</v>
+        <v>1.895</v>
       </c>
       <c r="F3" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.045999999999999999</v>
       </c>
       <c r="G3" s="9">
-        <v>97.588999999999999</v>
+        <v>97.587999999999994</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4">
       <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11">
-        <v>51.67</v>
+        <v>51.417999999999999</v>
       </c>
       <c r="C4" s="11">
-        <v>4.657</v>
+        <v>4.6559999999999997</v>
       </c>
       <c r="D4" s="11">
-        <v>90.988</v>
+        <v>90.945999999999998</v>
       </c>
       <c r="E4" s="11">
-        <v>358.99599999999998</v>
+        <v>356.99599999999998</v>
       </c>
       <c r="F4" s="11">
-        <v>310.21600000000001</v>
+        <v>302.88</v>
       </c>
       <c r="G4" s="12">
-        <v>13.587999999999999</v>
+        <v>15.159000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_rms_summary.xlsx
+++ b/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_rms_summary.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="10">
   <si>
     <t>Frequency Band</t>
   </si>
@@ -593,13 +593,13 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="1" max="1" width="15.84375" bestFit="true" customWidth="true"/>
-    <col min="2" max="2" width="15.15234375" bestFit="true" customWidth="true"/>
-    <col min="3" max="3" width="13.765625" bestFit="true" customWidth="true"/>
-    <col min="4" max="4" width="14" bestFit="true" customWidth="true"/>
-    <col min="5" max="5" width="16.61328125" bestFit="true" customWidth="true"/>
-    <col min="6" max="6" width="15.23046875" bestFit="true" customWidth="true"/>
-    <col min="7" max="7" width="14" bestFit="true" customWidth="true"/>
+    <col min="1" max="1" width="17" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="16.140625" bestFit="true" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" bestFit="true" customWidth="true"/>
+    <col min="4" max="4" width="15" bestFit="true" customWidth="true"/>
+    <col min="5" max="5" width="17.5703125" bestFit="true" customWidth="true"/>
+    <col min="6" max="6" width="16.140625" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="15" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.3" thickBot="true">
@@ -653,22 +653,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="8">
-        <v>15.624000000000001</v>
+        <v>15.444000000000001</v>
       </c>
       <c r="C3" s="8">
-        <v>0.36199999999999999</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="D3" s="8">
-        <v>97.685000000000002</v>
+        <v>97.692999999999998</v>
       </c>
       <c r="E3" s="8">
-        <v>1.895</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="F3" s="8">
-        <v>0.045999999999999999</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="G3" s="9">
-        <v>97.587999999999994</v>
+        <v>97.597999999999999</v>
       </c>
     </row>
     <row r="4">

--- a/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_rms_summary.xlsx
+++ b/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_rms_summary.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="50" uniqueCount="10">
   <si>
     <t>Frequency Band</t>
   </si>
